--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126812964</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126813131</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>126814298</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>126814579</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>126813856</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126812303</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126814242</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1709,54 +1709,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126813039</v>
+        <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>98265</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441258</v>
+        <v>441294</v>
       </c>
       <c r="R11" t="n">
-        <v>6763357</v>
+        <v>6763405</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1788,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1814,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1828,7 +1824,7 @@
         <v>126812997</v>
       </c>
       <c r="B12" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,45 +1942,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>98340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R13" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,52 +2051,57 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812497</v>
+        <v>126812386</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441403</v>
+        <v>441474</v>
       </c>
       <c r="R14" t="n">
-        <v>6763486</v>
+        <v>6763493</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2143,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,45 +2175,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812622</v>
+        <v>126814587</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441348</v>
+        <v>441468</v>
       </c>
       <c r="R15" t="n">
-        <v>6763465</v>
+        <v>6763484</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2235,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,12 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,17 +2280,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812345</v>
+        <v>126812622</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,14 +2318,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441501</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6763508</v>
+        <v>6763465</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2347,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2367,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt på tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,50 +2399,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812386</v>
+        <v>126812497</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441474</v>
+        <v>441403</v>
       </c>
       <c r="R17" t="n">
-        <v>6763493</v>
+        <v>6763486</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,50 +2506,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126814587</v>
+        <v>126812345</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441468</v>
+        <v>441501</v>
       </c>
       <c r="R18" t="n">
-        <v>6763484</v>
+        <v>6763508</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126813866</v>
+        <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2629,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441112</v>
+        <v>441451</v>
       </c>
       <c r="R19" t="n">
-        <v>6763178</v>
+        <v>6763480</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2698,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126814541</v>
+        <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,34 +2741,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441451</v>
+        <v>441112</v>
       </c>
       <c r="R20" t="n">
-        <v>6763480</v>
+        <v>6763178</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2795,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,12 +2810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,7 +2840,7 @@
         <v>126813605</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>126813199</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126814216</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126812964</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126813131</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>126814298</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>126814579</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>126813856</v>
       </c>
       <c r="B6" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126812303</v>
       </c>
       <c r="B7" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126814242</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126812997</v>
+        <v>126813039</v>
       </c>
       <c r="B12" t="n">
-        <v>98457</v>
+        <v>98346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,36 +1832,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1870,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441264</v>
+        <v>441258</v>
       </c>
       <c r="R12" t="n">
-        <v>6763358</v>
+        <v>6763357</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1905,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126813039</v>
+        <v>126812997</v>
       </c>
       <c r="B13" t="n">
-        <v>98340</v>
+        <v>98463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,31 +1948,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441258</v>
+        <v>441264</v>
       </c>
       <c r="R13" t="n">
-        <v>6763357</v>
+        <v>6763358</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812386</v>
+        <v>126814587</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,27 +2069,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441474</v>
+        <v>441468</v>
       </c>
       <c r="R14" t="n">
-        <v>6763493</v>
+        <v>6763484</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,57 +2163,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126814587</v>
+        <v>126812622</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441468</v>
+        <v>441348</v>
       </c>
       <c r="R15" t="n">
-        <v>6763484</v>
+        <v>6763465</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2250,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2250,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,17 +2275,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812622</v>
+        <v>126812497</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,14 +2313,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441403</v>
       </c>
       <c r="R16" t="n">
-        <v>6763465</v>
+        <v>6763486</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,12 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812497</v>
+        <v>126812345</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441403</v>
+        <v>441501</v>
       </c>
       <c r="R17" t="n">
-        <v>6763486</v>
+        <v>6763508</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2469,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,45 +2501,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812345</v>
+        <v>126812386</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441501</v>
+        <v>441474</v>
       </c>
       <c r="R18" t="n">
-        <v>6763508</v>
+        <v>6763493</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Riktigt på tallstammar</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,7 +2621,7 @@
         <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>126813605</v>
       </c>
       <c r="B21" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>126813199</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,45 +3065,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126813524</v>
+        <v>126814216</v>
       </c>
       <c r="B23" t="n">
-        <v>78678</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441243</v>
+        <v>441328</v>
       </c>
       <c r="R23" t="n">
-        <v>6763262</v>
+        <v>6763356</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3135,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3154,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814513</v>
+        <v>126813524</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>78681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441451</v>
+        <v>441243</v>
       </c>
       <c r="R24" t="n">
-        <v>6763480</v>
+        <v>6763262</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,12 +3266,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,54 +3293,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814216</v>
+        <v>126814513</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441328</v>
+        <v>441451</v>
       </c>
       <c r="R25" t="n">
-        <v>6763356</v>
+        <v>6763480</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -1709,45 +1709,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R11" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1779,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,61 +1818,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126813039</v>
+        <v>126812671</v>
       </c>
       <c r="B12" t="n">
-        <v>98346</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441258</v>
+        <v>441294</v>
       </c>
       <c r="R12" t="n">
-        <v>6763357</v>
+        <v>6763405</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2170,45 +2170,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812622</v>
+        <v>126812386</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441348</v>
+        <v>441474</v>
       </c>
       <c r="R15" t="n">
-        <v>6763465</v>
+        <v>6763493</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2240,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,12 +2255,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,7 +2287,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812497</v>
+        <v>126812622</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2313,14 +2318,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441403</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6763486</v>
+        <v>6763465</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2367,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,7 +2399,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812345</v>
+        <v>126812497</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2424,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441501</v>
+        <v>441403</v>
       </c>
       <c r="R17" t="n">
-        <v>6763508</v>
+        <v>6763486</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2459,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,50 +2506,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812386</v>
+        <v>126812345</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441474</v>
+        <v>441501</v>
       </c>
       <c r="R18" t="n">
-        <v>6763493</v>
+        <v>6763508</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Tjäderbetat tall</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126814541</v>
+        <v>126813866</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2629,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441451</v>
+        <v>441112</v>
       </c>
       <c r="R19" t="n">
-        <v>6763480</v>
+        <v>6763178</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,12 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126813866</v>
+        <v>126814541</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,34 +2736,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441112</v>
+        <v>441451</v>
       </c>
       <c r="R20" t="n">
-        <v>6763178</v>
+        <v>6763480</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2800,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2805,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3065,54 +3065,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126814216</v>
+        <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441328</v>
+        <v>441243</v>
       </c>
       <c r="R23" t="n">
-        <v>6763356</v>
+        <v>6763262</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3144,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3154,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126813524</v>
+        <v>126814513</v>
       </c>
       <c r="B24" t="n">
-        <v>78681</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,34 +3183,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441243</v>
+        <v>441451</v>
       </c>
       <c r="R24" t="n">
-        <v>6763262</v>
+        <v>6763480</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3256,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,7 +3257,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,50 +3289,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814513</v>
+        <v>126814216</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441451</v>
+        <v>441328</v>
       </c>
       <c r="R25" t="n">
-        <v>6763480</v>
+        <v>6763356</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814587</v>
+        <v>126812386</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,27 +2069,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441468</v>
+        <v>441474</v>
       </c>
       <c r="R14" t="n">
-        <v>6763484</v>
+        <v>6763493</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2143,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,57 +2168,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812386</v>
+        <v>126812622</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441474</v>
+        <v>441348</v>
       </c>
       <c r="R15" t="n">
-        <v>6763493</v>
+        <v>6763465</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tjäderbetat tall</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,7 +2287,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812622</v>
+        <v>126812497</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2318,14 +2318,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441403</v>
       </c>
       <c r="R16" t="n">
-        <v>6763465</v>
+        <v>6763486</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,12 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,7 +2394,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812497</v>
+        <v>126812345</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441403</v>
+        <v>441501</v>
       </c>
       <c r="R17" t="n">
-        <v>6763486</v>
+        <v>6763508</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2469,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2474,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,45 +2506,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812345</v>
+        <v>126814587</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441501</v>
+        <v>441468</v>
       </c>
       <c r="R18" t="n">
-        <v>6763508</v>
+        <v>6763484</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126813866</v>
+        <v>126813605</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441112</v>
+        <v>441221</v>
       </c>
       <c r="R19" t="n">
-        <v>6763178</v>
+        <v>6763228</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813605</v>
+        <v>126813866</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441221</v>
+        <v>441112</v>
       </c>
       <c r="R21" t="n">
-        <v>6763228</v>
+        <v>6763178</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126812964</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126813131</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>126814298</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126814242</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1709,54 +1709,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126813039</v>
+        <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>98346</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441258</v>
+        <v>441294</v>
       </c>
       <c r="R11" t="n">
-        <v>6763357</v>
+        <v>6763405</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1788,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,52 +1814,61 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R12" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1895,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1940,7 +1940,7 @@
         <v>126812997</v>
       </c>
       <c r="B13" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,50 +2058,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812386</v>
+        <v>126812497</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441474</v>
+        <v>441403</v>
       </c>
       <c r="R14" t="n">
-        <v>6763493</v>
+        <v>6763486</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,12 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812622</v>
+        <v>126812345</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2206,14 +2196,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441348</v>
+        <v>441501</v>
       </c>
       <c r="R15" t="n">
-        <v>6763465</v>
+        <v>6763508</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2245,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2245,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812497</v>
+        <v>126812622</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2318,14 +2308,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441403</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6763486</v>
+        <v>6763465</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2357,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,45 +2389,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812345</v>
+        <v>126812386</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441501</v>
+        <v>441474</v>
       </c>
       <c r="R17" t="n">
-        <v>6763508</v>
+        <v>6763493</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt på tallstammar</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126813605</v>
+        <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2629,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441221</v>
+        <v>441451</v>
       </c>
       <c r="R19" t="n">
-        <v>6763228</v>
+        <v>6763480</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2698,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126814541</v>
+        <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,34 +2741,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441451</v>
+        <v>441112</v>
       </c>
       <c r="R20" t="n">
-        <v>6763480</v>
+        <v>6763178</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2795,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,12 +2810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813866</v>
+        <v>126813605</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441112</v>
+        <v>441221</v>
       </c>
       <c r="R21" t="n">
-        <v>6763178</v>
+        <v>6763228</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,7 +2947,7 @@
         <v>126813199</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126813524</v>
+        <v>126814513</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,34 +3076,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441243</v>
+        <v>441451</v>
       </c>
       <c r="R23" t="n">
-        <v>6763262</v>
+        <v>6763480</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3135,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3150,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,50 +3182,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814513</v>
+        <v>126814216</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441451</v>
+        <v>441328</v>
       </c>
       <c r="R24" t="n">
-        <v>6763480</v>
+        <v>6763356</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3247,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,12 +3271,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,54 +3303,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814216</v>
+        <v>126813524</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441328</v>
+        <v>441243</v>
       </c>
       <c r="R25" t="n">
-        <v>6763356</v>
+        <v>6763262</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3368,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3383,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -2389,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812386</v>
+        <v>126814587</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,27 +2400,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441474</v>
+        <v>441468</v>
       </c>
       <c r="R17" t="n">
-        <v>6763493</v>
+        <v>6763484</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,12 +2474,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,17 +2494,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126814587</v>
+        <v>126812386</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,27 +2512,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441468</v>
+        <v>441474</v>
       </c>
       <c r="R18" t="n">
-        <v>6763484</v>
+        <v>6763493</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126814541</v>
+        <v>126813605</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2629,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441451</v>
+        <v>441221</v>
       </c>
       <c r="R19" t="n">
-        <v>6763480</v>
+        <v>6763228</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,12 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126813866</v>
+        <v>126814541</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,34 +2736,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441112</v>
+        <v>441451</v>
       </c>
       <c r="R20" t="n">
-        <v>6763178</v>
+        <v>6763480</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2800,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2805,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813605</v>
+        <v>126813866</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441221</v>
+        <v>441112</v>
       </c>
       <c r="R21" t="n">
-        <v>6763228</v>
+        <v>6763178</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -1709,45 +1709,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R11" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1779,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,61 +1818,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126813039</v>
+        <v>126812671</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441258</v>
+        <v>441294</v>
       </c>
       <c r="R12" t="n">
-        <v>6763357</v>
+        <v>6763405</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812497</v>
+        <v>126812622</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -2089,14 +2089,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441403</v>
+        <v>441348</v>
       </c>
       <c r="R14" t="n">
-        <v>6763486</v>
+        <v>6763465</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812345</v>
+        <v>126812497</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2200,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441501</v>
+        <v>441403</v>
       </c>
       <c r="R15" t="n">
-        <v>6763508</v>
+        <v>6763486</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2235,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,12 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812622</v>
+        <v>126812345</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2308,14 +2308,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441501</v>
       </c>
       <c r="R16" t="n">
-        <v>6763465</v>
+        <v>6763508</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126814587</v>
+        <v>126812386</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,27 +2400,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441468</v>
+        <v>441474</v>
       </c>
       <c r="R17" t="n">
-        <v>6763484</v>
+        <v>6763493</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2474,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,17 +2499,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812386</v>
+        <v>126814587</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,27 +2517,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441474</v>
+        <v>441468</v>
       </c>
       <c r="R18" t="n">
-        <v>6763493</v>
+        <v>6763484</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126813605</v>
+        <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2629,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441221</v>
+        <v>441451</v>
       </c>
       <c r="R19" t="n">
-        <v>6763228</v>
+        <v>6763480</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2698,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126814541</v>
+        <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,34 +2741,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441451</v>
+        <v>441112</v>
       </c>
       <c r="R20" t="n">
-        <v>6763480</v>
+        <v>6763178</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2795,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,12 +2810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813866</v>
+        <v>126813605</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441112</v>
+        <v>441221</v>
       </c>
       <c r="R21" t="n">
-        <v>6763178</v>
+        <v>6763228</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126814513</v>
+        <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,39 +3076,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441451</v>
+        <v>441243</v>
       </c>
       <c r="R23" t="n">
-        <v>6763480</v>
+        <v>6763262</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3140,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,54 +3172,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814216</v>
+        <v>126814513</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441328</v>
+        <v>441451</v>
       </c>
       <c r="R24" t="n">
-        <v>6763356</v>
+        <v>6763480</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3261,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,12 +3257,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,45 +3289,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126813524</v>
+        <v>126814216</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441243</v>
+        <v>441328</v>
       </c>
       <c r="R25" t="n">
-        <v>6763262</v>
+        <v>6763356</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3373,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,7 +3378,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -1709,54 +1709,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126813039</v>
+        <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441258</v>
+        <v>441294</v>
       </c>
       <c r="R11" t="n">
-        <v>6763357</v>
+        <v>6763405</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1788,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,52 +1814,61 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R12" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1895,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2058,45 +2058,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812622</v>
+        <v>126814587</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441348</v>
+        <v>441468</v>
       </c>
       <c r="R14" t="n">
-        <v>6763465</v>
+        <v>6763484</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812497</v>
+        <v>126812622</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2201,14 +2201,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441403</v>
+        <v>441348</v>
       </c>
       <c r="R15" t="n">
-        <v>6763486</v>
+        <v>6763465</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2250,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,7 +2282,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812345</v>
+        <v>126812497</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441501</v>
+        <v>441403</v>
       </c>
       <c r="R16" t="n">
-        <v>6763508</v>
+        <v>6763486</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,50 +2389,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812386</v>
+        <v>126812345</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441474</v>
+        <v>441501</v>
       </c>
       <c r="R17" t="n">
-        <v>6763493</v>
+        <v>6763508</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Tjäderbetat tall</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126814587</v>
+        <v>126812386</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,27 +2512,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441468</v>
+        <v>441474</v>
       </c>
       <c r="R18" t="n">
-        <v>6763484</v>
+        <v>6763493</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126812964</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126813131</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>126814298</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>126814579</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>126813856</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126812303</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126814242</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>126814445</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126812560</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,45 +1709,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R11" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1779,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,17 +1818,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126813039</v>
+        <v>126812997</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,31 +1836,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1865,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441258</v>
+        <v>441264</v>
       </c>
       <c r="R12" t="n">
-        <v>6763357</v>
+        <v>6763358</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1900,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,59 +1946,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126812997</v>
+        <v>126812671</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441264</v>
+        <v>441294</v>
       </c>
       <c r="R13" t="n">
-        <v>6763358</v>
+        <v>6763405</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2021,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2026,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
         <v>126814587</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>126812622</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>126812497</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>126812345</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126812386</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>126813605</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>126813199</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126813524</v>
+        <v>126814513</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,34 +3076,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441243</v>
+        <v>441451</v>
       </c>
       <c r="R23" t="n">
-        <v>6763262</v>
+        <v>6763480</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3135,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3150,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814513</v>
+        <v>126813524</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>78685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,39 +3193,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441451</v>
+        <v>441243</v>
       </c>
       <c r="R24" t="n">
-        <v>6763480</v>
+        <v>6763262</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3247,7 +3252,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,12 +3262,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,7 +3292,7 @@
         <v>126814216</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>126814383</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -1709,54 +1709,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126813039</v>
+        <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>98351</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441258</v>
+        <v>441294</v>
       </c>
       <c r="R11" t="n">
-        <v>6763357</v>
+        <v>6763405</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1788,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1814,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1946,45 +1942,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126812671</v>
+        <v>126813039</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441294</v>
+        <v>441258</v>
       </c>
       <c r="R13" t="n">
-        <v>6763405</v>
+        <v>6763357</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,57 +2051,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814587</v>
+        <v>126812622</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441468</v>
+        <v>441348</v>
       </c>
       <c r="R14" t="n">
-        <v>6763484</v>
+        <v>6763465</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812622</v>
+        <v>126812497</v>
       </c>
       <c r="B15" t="n">
         <v>79018</v>
@@ -2201,14 +2201,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441348</v>
+        <v>441403</v>
       </c>
       <c r="R15" t="n">
-        <v>6763465</v>
+        <v>6763486</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,12 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812497</v>
+        <v>126812345</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441403</v>
+        <v>441501</v>
       </c>
       <c r="R16" t="n">
-        <v>6763486</v>
+        <v>6763508</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,45 +2389,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812345</v>
+        <v>126812386</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441501</v>
+        <v>441474</v>
       </c>
       <c r="R17" t="n">
-        <v>6763508</v>
+        <v>6763493</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2459,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2474,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt på tallstammar</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812386</v>
+        <v>126814587</v>
       </c>
       <c r="B18" t="n">
-        <v>56853</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,27 +2517,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441474</v>
+        <v>441468</v>
       </c>
       <c r="R18" t="n">
-        <v>6763493</v>
+        <v>6763484</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126814541</v>
+        <v>126813605</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2629,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441451</v>
+        <v>441221</v>
       </c>
       <c r="R19" t="n">
-        <v>6763480</v>
+        <v>6763228</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,12 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126813866</v>
+        <v>126814541</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,34 +2736,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441112</v>
+        <v>441451</v>
       </c>
       <c r="R20" t="n">
-        <v>6763178</v>
+        <v>6763480</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2800,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2805,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813605</v>
+        <v>126813866</v>
       </c>
       <c r="B21" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441221</v>
+        <v>441112</v>
       </c>
       <c r="R21" t="n">
-        <v>6763228</v>
+        <v>6763178</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126814513</v>
+        <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,39 +3076,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441451</v>
+        <v>441243</v>
       </c>
       <c r="R23" t="n">
-        <v>6763480</v>
+        <v>6763262</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3140,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3150,12 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126813524</v>
+        <v>126814513</v>
       </c>
       <c r="B24" t="n">
-        <v>78685</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,34 +3183,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441243</v>
+        <v>441451</v>
       </c>
       <c r="R24" t="n">
-        <v>6763262</v>
+        <v>6763480</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3252,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3262,7 +3257,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -2058,45 +2058,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812622</v>
+        <v>126814587</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441348</v>
+        <v>441468</v>
       </c>
       <c r="R14" t="n">
-        <v>6763465</v>
+        <v>6763484</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,52 +2163,57 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812497</v>
+        <v>126812386</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441403</v>
+        <v>441474</v>
       </c>
       <c r="R15" t="n">
-        <v>6763486</v>
+        <v>6763493</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2240,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2255,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,7 +2287,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812345</v>
+        <v>126812622</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2308,14 +2318,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441501</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6763508</v>
+        <v>6763465</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2347,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2367,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt på tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,50 +2399,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812386</v>
+        <v>126812497</v>
       </c>
       <c r="B17" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441474</v>
+        <v>441403</v>
       </c>
       <c r="R17" t="n">
-        <v>6763493</v>
+        <v>6763486</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,50 +2506,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126814587</v>
+        <v>126812345</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441468</v>
+        <v>441501</v>
       </c>
       <c r="R18" t="n">
-        <v>6763484</v>
+        <v>6763508</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3065,45 +3065,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126813524</v>
+        <v>126814216</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441243</v>
+        <v>441328</v>
       </c>
       <c r="R23" t="n">
-        <v>6763262</v>
+        <v>6763356</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3135,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3154,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814513</v>
+        <v>126813524</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>78685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,39 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441451</v>
+        <v>441243</v>
       </c>
       <c r="R24" t="n">
-        <v>6763480</v>
+        <v>6763262</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,12 +3266,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,54 +3293,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814216</v>
+        <v>126814513</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441328</v>
+        <v>441451</v>
       </c>
       <c r="R25" t="n">
-        <v>6763356</v>
+        <v>6763480</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -2058,50 +2058,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814587</v>
+        <v>126812622</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441468</v>
+        <v>441348</v>
       </c>
       <c r="R14" t="n">
-        <v>6763484</v>
+        <v>6763465</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,57 +2163,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812386</v>
+        <v>126812497</v>
       </c>
       <c r="B15" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441474</v>
+        <v>441403</v>
       </c>
       <c r="R15" t="n">
-        <v>6763493</v>
+        <v>6763486</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2245,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812622</v>
+        <v>126812345</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2318,14 +2308,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441501</v>
       </c>
       <c r="R16" t="n">
-        <v>6763465</v>
+        <v>6763508</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2357,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,12 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,45 +2389,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812497</v>
+        <v>126814587</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441403</v>
+        <v>441468</v>
       </c>
       <c r="R17" t="n">
-        <v>6763486</v>
+        <v>6763484</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2469,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2474,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,17 +2494,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812345</v>
+        <v>126813605</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,34 +2512,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441501</v>
+        <v>441221</v>
       </c>
       <c r="R18" t="n">
-        <v>6763508</v>
+        <v>6763228</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2581,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,17 +2601,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126813605</v>
+        <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,34 +2619,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441221</v>
+        <v>441451</v>
       </c>
       <c r="R19" t="n">
-        <v>6763228</v>
+        <v>6763480</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2688,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2688,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126814541</v>
+        <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,34 +2731,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441451</v>
+        <v>441112</v>
       </c>
       <c r="R20" t="n">
-        <v>6763480</v>
+        <v>6763178</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2795,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,12 +2800,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,45 +2827,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813866</v>
+        <v>126813199</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441112</v>
+        <v>441274</v>
       </c>
       <c r="R21" t="n">
-        <v>6763178</v>
+        <v>6763367</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2916,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4 blomstängel</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,7 +2948,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126813199</v>
+        <v>126814216</v>
       </c>
       <c r="B22" t="n">
         <v>98447</v>
@@ -2974,7 +2978,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2988,10 +2992,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441274</v>
+        <v>441328</v>
       </c>
       <c r="R22" t="n">
-        <v>6763367</v>
+        <v>6763356</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3023,7 +3027,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3037,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>4 blomstängel</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,54 +3069,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126814216</v>
+        <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441328</v>
+        <v>441243</v>
       </c>
       <c r="R23" t="n">
-        <v>6763356</v>
+        <v>6763262</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3154,12 +3149,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3176,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126813524</v>
+        <v>126814513</v>
       </c>
       <c r="B24" t="n">
-        <v>78685</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,34 +3187,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441243</v>
+        <v>441451</v>
       </c>
       <c r="R24" t="n">
-        <v>6763262</v>
+        <v>6763480</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,7 +3261,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814513</v>
+        <v>126814383</v>
       </c>
       <c r="B25" t="n">
         <v>57661</v>
@@ -3322,21 +3322,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441451</v>
+        <v>441357</v>
       </c>
       <c r="R25" t="n">
-        <v>6763480</v>
+        <v>6763394</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3368,7 +3371,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3381,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,53 +3413,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126814383</v>
+        <v>126812386</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441357</v>
+        <v>441474</v>
       </c>
       <c r="R26" t="n">
-        <v>6763394</v>
+        <v>6763493</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -3416,7 +3416,7 @@
         <v>126812386</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -3416,7 +3416,7 @@
         <v>126812386</v>
       </c>
       <c r="B26" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -3416,7 +3416,7 @@
         <v>126812386</v>
       </c>
       <c r="B26" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126812964</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126813131</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>126814298</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>126814579</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>126813856</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126812303</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126814242</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>126814445</v>
       </c>
       <c r="B9" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126812560</v>
       </c>
       <c r="B10" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>126812997</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>126813039</v>
       </c>
       <c r="B13" t="n">
-        <v>98351</v>
+        <v>98340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,45 +2058,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812622</v>
+        <v>126812386</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>56864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441348</v>
+        <v>441474</v>
       </c>
       <c r="R14" t="n">
-        <v>6763465</v>
+        <v>6763493</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2143,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,45 +2175,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812497</v>
+        <v>126814587</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441403</v>
+        <v>441468</v>
       </c>
       <c r="R15" t="n">
-        <v>6763486</v>
+        <v>6763484</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2240,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,17 +2280,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812345</v>
+        <v>126812622</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,14 +2318,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441501</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6763508</v>
+        <v>6763465</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2347,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2367,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt på tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,50 +2399,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126814587</v>
+        <v>126812497</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441468</v>
+        <v>441403</v>
       </c>
       <c r="R17" t="n">
-        <v>6763484</v>
+        <v>6763486</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2464,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,17 +2499,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126813605</v>
+        <v>126812345</v>
       </c>
       <c r="B18" t="n">
-        <v>78777</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,34 +2517,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441221</v>
+        <v>441501</v>
       </c>
       <c r="R18" t="n">
-        <v>6763228</v>
+        <v>6763508</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2571,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,7 +2611,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2611,7 +2621,7 @@
         <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2723,7 +2733,7 @@
         <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,54 +2837,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813199</v>
+        <v>126813605</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>78770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441274</v>
+        <v>441221</v>
       </c>
       <c r="R21" t="n">
-        <v>6763367</v>
+        <v>6763228</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2906,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,12 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>4 blomstängel</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2944,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126814216</v>
+        <v>126813199</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,7 +2974,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2992,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441328</v>
+        <v>441274</v>
       </c>
       <c r="R22" t="n">
-        <v>6763356</v>
+        <v>6763367</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3027,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3037,12 +3033,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>4 blomstängel</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,7 +3068,7 @@
         <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3179,7 +3175,7 @@
         <v>126814513</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,53 +3289,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814383</v>
+        <v>126814216</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441357</v>
+        <v>441328</v>
       </c>
       <c r="R25" t="n">
-        <v>6763394</v>
+        <v>6763356</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3371,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3381,12 +3378,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,50 +3410,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126812386</v>
+        <v>126814383</v>
       </c>
       <c r="B26" t="n">
-        <v>56864</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441474</v>
+        <v>441357</v>
       </c>
       <c r="R26" t="n">
-        <v>6763493</v>
+        <v>6763394</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Tjäderbetat tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126812964</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126813131</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>126814298</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>126814579</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>126813856</v>
       </c>
       <c r="B6" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126812303</v>
       </c>
       <c r="B7" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126814242</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>126814445</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126812560</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>126812671</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>126812997</v>
       </c>
       <c r="B12" t="n">
-        <v>98457</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>126813039</v>
       </c>
       <c r="B13" t="n">
-        <v>98340</v>
+        <v>98351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,50 +2058,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812386</v>
+        <v>126812622</v>
       </c>
       <c r="B14" t="n">
-        <v>56864</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441474</v>
+        <v>441348</v>
       </c>
       <c r="R14" t="n">
-        <v>6763493</v>
+        <v>6763465</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,12 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Tjäderbetat tall</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,50 +2170,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126814587</v>
+        <v>126812497</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441468</v>
+        <v>441403</v>
       </c>
       <c r="R15" t="n">
-        <v>6763484</v>
+        <v>6763486</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2250,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,17 +2270,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812622</v>
+        <v>126812345</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,14 +2308,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441501</v>
       </c>
       <c r="R16" t="n">
-        <v>6763465</v>
+        <v>6763508</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2357,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,12 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,45 +2389,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126812497</v>
+        <v>126814587</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441403</v>
+        <v>441468</v>
       </c>
       <c r="R17" t="n">
-        <v>6763486</v>
+        <v>6763484</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2469,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2474,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,17 +2494,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126812345</v>
+        <v>126813605</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>78777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,34 +2512,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441501</v>
+        <v>441221</v>
       </c>
       <c r="R18" t="n">
-        <v>6763508</v>
+        <v>6763228</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2576,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2581,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,7 +2601,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2621,7 +2611,7 @@
         <v>126814541</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2723,7 @@
         <v>126813866</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,45 +2827,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126813605</v>
+        <v>126813199</v>
       </c>
       <c r="B21" t="n">
-        <v>78770</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441221</v>
+        <v>441274</v>
       </c>
       <c r="R21" t="n">
-        <v>6763228</v>
+        <v>6763367</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2907,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2916,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4 blomstängel</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126813199</v>
+        <v>126814216</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2978,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2988,10 +2992,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441274</v>
+        <v>441328</v>
       </c>
       <c r="R22" t="n">
-        <v>6763367</v>
+        <v>6763356</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3023,7 +3027,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3037,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>4 blomstängel</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,7 +3072,7 @@
         <v>126813524</v>
       </c>
       <c r="B23" t="n">
-        <v>78678</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3179,7 @@
         <v>126814513</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,54 +3293,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814216</v>
+        <v>126814383</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441328</v>
+        <v>441357</v>
       </c>
       <c r="R25" t="n">
-        <v>6763356</v>
+        <v>6763394</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3368,7 +3371,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3381,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,53 +3413,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126814383</v>
+        <v>126812386</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>56864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441357</v>
+        <v>441474</v>
       </c>
       <c r="R26" t="n">
-        <v>6763394</v>
+        <v>6763493</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126812964</v>
+        <v>126813524</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441264</v>
+        <v>441243</v>
       </c>
       <c r="R2" t="n">
-        <v>6763358</v>
+        <v>6763262</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 blommande</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126813131</v>
+        <v>126812345</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,48 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441331</v>
+        <v>441501</v>
       </c>
       <c r="R3" t="n">
-        <v>6763333</v>
+        <v>6763508</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -880,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 blomstängel</t>
+          <t>Riktigt på tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,17 +887,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126814298</v>
+        <v>126812497</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,43 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441355</v>
+        <v>441403</v>
       </c>
       <c r="R4" t="n">
-        <v>6763391</v>
+        <v>6763486</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1001,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 blommor</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,21 +994,21 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814579</v>
+        <v>126812622</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1074,14 +1032,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441468</v>
+        <v>441348</v>
       </c>
       <c r="R5" t="n">
-        <v>6763484</v>
+        <v>6763465</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1113,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,39 +1106,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126813856</v>
+        <v>126812671</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441112</v>
+        <v>441294</v>
       </c>
       <c r="R6" t="n">
-        <v>6763178</v>
+        <v>6763405</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1220,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,39 +1218,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126812303</v>
+        <v>126814541</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441506</v>
+        <v>441451</v>
       </c>
       <c r="R7" t="n">
-        <v>6763514</v>
+        <v>6763480</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1327,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,17 +1330,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814242</v>
+        <v>126814579</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,43 +1348,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441321</v>
+        <v>441468</v>
       </c>
       <c r="R8" t="n">
-        <v>6763376</v>
+        <v>6763484</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1443,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,12 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>7 blommor</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,50 +1444,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814445</v>
+        <v>126813866</v>
       </c>
       <c r="B9" t="n">
-        <v>56853</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441331</v>
+        <v>441112</v>
       </c>
       <c r="R9" t="n">
-        <v>6763426</v>
+        <v>6763178</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1560,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,50 +1551,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126812560</v>
+        <v>126814383</v>
       </c>
       <c r="B10" t="n">
-        <v>56853</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441419</v>
+        <v>441357</v>
       </c>
       <c r="R10" t="n">
-        <v>6763466</v>
+        <v>6763394</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1672,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1639,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,17 +1664,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126812671</v>
+        <v>126814513</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,34 +1682,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441294</v>
+        <v>441451</v>
       </c>
       <c r="R11" t="n">
-        <v>6763405</v>
+        <v>6763480</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1779,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1756,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,17 +1781,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126812997</v>
+        <v>126812386</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,48 +1799,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441264</v>
+        <v>441474</v>
       </c>
       <c r="R12" t="n">
-        <v>6763358</v>
+        <v>6763493</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1905,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1873,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,17 +1898,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126813039</v>
+        <v>126812560</v>
       </c>
       <c r="B13" t="n">
-        <v>98351</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,43 +1916,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441258</v>
+        <v>441419</v>
       </c>
       <c r="R13" t="n">
-        <v>6763357</v>
+        <v>6763466</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2021,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,52 +2010,57 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126812622</v>
+        <v>126814445</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441348</v>
+        <v>441331</v>
       </c>
       <c r="R14" t="n">
-        <v>6763465</v>
+        <v>6763426</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2128,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,55 +2122,84 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126812497</v>
+        <v>66754627</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>58829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>w13G_x08, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441403</v>
+        <v>441552</v>
       </c>
       <c r="R15" t="n">
-        <v>6763486</v>
+        <v>6763455</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2233,24 +2221,34 @@
           <t>Vänjan</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>w13G_x08</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2007-06-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2007-06-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lufttemperatur: 12 grader</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,57 +2263,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Mattias Sterner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Mattias Sterner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av större vattensalamander</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126812345</v>
+        <v>126814587</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441501</v>
+        <v>441468</v>
       </c>
       <c r="R16" t="n">
-        <v>6763508</v>
+        <v>6763484</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2347,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riktigt på tallstammar</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Lena Thommson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126814587</v>
+        <v>66765845</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>58826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,42 +2402,61 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>208242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>w13G_x08, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441468</v>
+        <v>441552</v>
       </c>
       <c r="R17" t="n">
-        <v>6763484</v>
+        <v>6763455</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2457,24 +2478,34 @@
           <t>Vänjan</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>w13G_x08</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2007-06-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2007-06-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lufttemperatur: 12 grader</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,57 +2520,70 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Mattias Sterner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Mattias Sterner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av större vattensalamander</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126813605</v>
+        <v>126813039</v>
       </c>
       <c r="B18" t="n">
-        <v>78777</v>
+        <v>99022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441221</v>
+        <v>441258</v>
       </c>
       <c r="R18" t="n">
-        <v>6763228</v>
+        <v>6763357</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2571,7 +2615,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2625,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,45 +2652,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126814541</v>
+        <v>126812964</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441451</v>
+        <v>441264</v>
       </c>
       <c r="R19" t="n">
-        <v>6763480</v>
+        <v>6763358</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2678,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2688,12 +2741,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>3 blommande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,45 +2773,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126813866</v>
+        <v>126813131</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441112</v>
+        <v>441331</v>
       </c>
       <c r="R20" t="n">
-        <v>6763178</v>
+        <v>6763333</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2790,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2867,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 blomstängel</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,7 +2902,7 @@
         <v>126813199</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +3023,7 @@
         <v>126814216</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,45 +3141,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126813524</v>
+        <v>126814242</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441243</v>
+        <v>441321</v>
       </c>
       <c r="R23" t="n">
-        <v>6763262</v>
+        <v>6763376</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3139,7 +3220,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3149,7 +3230,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>7 blommor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,50 +3262,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814513</v>
+        <v>126814298</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Turlok, Turlok, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441451</v>
+        <v>441355</v>
       </c>
       <c r="R24" t="n">
-        <v>6763480</v>
+        <v>6763391</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3251,7 +3341,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3261,12 +3351,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>10 blommor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,53 +3383,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814383</v>
+        <v>126812997</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441357</v>
+        <v>441264</v>
       </c>
       <c r="R25" t="n">
-        <v>6763394</v>
+        <v>6763358</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3371,7 +3467,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3381,12 +3477,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,50 +3504,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126812386</v>
+        <v>126812303</v>
       </c>
       <c r="B26" t="n">
-        <v>56864</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Turlok, Turlok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441474</v>
+        <v>441506</v>
       </c>
       <c r="R26" t="n">
-        <v>6763493</v>
+        <v>6763514</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3488,7 +3574,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3498,12 +3584,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,6 +3608,220 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126813605</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>441221</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6763228</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126813856</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>441112</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6763178</v>
+      </c>
+      <c r="S28" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34714-2025 artfynd.xlsx
+++ b/artfynd/A 34714-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812671</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814541</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814579</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813866</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814383</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814513</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,6 +1957,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812386</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812560</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814445</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2276,6 +2346,11 @@
           <t>Inventering av större vattensalamander</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66754627</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2388,6 +2463,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814587</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2533,6 +2613,11 @@
           <t>Inventering av större vattensalamander</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66765845</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2649,6 +2734,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813039</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2770,6 +2860,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812964</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2896,6 +2991,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813131</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3017,6 +3117,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813199</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3138,6 +3243,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814216</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3259,6 +3369,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814242</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3380,6 +3495,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126814298</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3501,6 +3621,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812997</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3608,6 +3733,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126812303</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3715,6 +3845,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813605</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3822,8 +3957,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126813856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>